--- a/Projeto/resultados_testes_estatisticos_v20251102-1210.xlsx
+++ b/Projeto/resultados_testes_estatisticos_v20251102-1210.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gilcesarf/git/repositories/imd/imd3002-202502/Projeto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA983242-CAF7-654C-845E-2226520A85F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B378DF39-DF20-4B4A-89B8-4524427178E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36200" yWindow="11400" windowWidth="34560" windowHeight="9780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="8380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumo_Geral" sheetId="1" r:id="rId1"/>
@@ -151,8 +151,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-* #,##0.000000000_-;\-* #,##0.000000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.000000000_-;\-* #,##0.000000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -194,8 +194,8 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/Projeto/resultados_testes_estatisticos_v20251102-1210.xlsx
+++ b/Projeto/resultados_testes_estatisticos_v20251102-1210.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gilcesarf/git/repositories/imd/imd3002-202502/Projeto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B378DF39-DF20-4B4A-89B8-4524427178E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2BEC6C-27AD-7446-A37A-188BA09FAF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="8380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34080" yWindow="14440" windowWidth="34560" windowHeight="21580" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumo_Geral" sheetId="1" r:id="rId1"/>
@@ -148,11 +148,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.000000000_-;\-* #,##0.000000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="190" formatCode="0.0000000000000000"/>
+    <numFmt numFmtId="194" formatCode="_-* #,##0.0000000000000000_-;\-* #,##0.0000000000000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -191,11 +190,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="194" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -506,8 +504,7 @@
     <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="19.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -571,7 +568,7 @@
       <c r="D2">
         <v>7.209326424870441</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>0.6153355838888005</v>
       </c>
       <c r="F2" t="s">
@@ -612,7 +609,7 @@
       <c r="D3">
         <v>6.2358778625953617</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>0.71609819863686019</v>
       </c>
       <c r="F3" t="s">
@@ -653,7 +650,7 @@
       <c r="D4">
         <v>24.150537634408579</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>5.698720869286655E-6</v>
       </c>
       <c r="F4" t="s">
@@ -694,7 +691,7 @@
       <c r="D5">
         <v>32.069331983805661</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>1.9370733297032321E-4</v>
       </c>
       <c r="F5" t="s">
@@ -732,11 +729,7 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.1640625" customWidth="1"/>
-    <col min="6" max="6" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -788,7 +781,7 @@
       <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>3.0991162591187279E-2</v>
       </c>
       <c r="F4" t="s">
@@ -808,7 +801,7 @@
       <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>3.9727329548266974E-6</v>
       </c>
       <c r="F5" t="s">
@@ -828,7 +821,7 @@
       <c r="D6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>8.3719467633767142E-3</v>
       </c>
       <c r="F6" t="s">
@@ -848,7 +841,7 @@
       <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>1.6584839573062001E-2</v>
       </c>
       <c r="F7" t="s">
@@ -868,7 +861,7 @@
       <c r="D8" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>7.0074238418840196E-3</v>
       </c>
       <c r="F8" t="s">
@@ -888,7 +881,7 @@
       <c r="D9" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>1.4039202332943311E-2</v>
       </c>
       <c r="F9" t="s">
@@ -904,6 +897,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="11" width="18.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -950,31 +946,31 @@
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>0.99999899999999997</v>
+        <v>0.99999914925619082</v>
       </c>
       <c r="D5" s="1">
-        <v>0.99982400000000005</v>
+        <v>0.99982440853336796</v>
       </c>
       <c r="E5" s="1">
-        <v>0.99967600000000001</v>
+        <v>0.99967579581709709</v>
       </c>
       <c r="F5" s="1">
-        <v>1</v>
+        <v>0.99999999820927599</v>
       </c>
       <c r="G5" s="1">
-        <v>1</v>
+        <v>0.99999989913505405</v>
       </c>
       <c r="H5" s="1">
-        <v>0.99999199999999999</v>
+        <v>0.99999234504534296</v>
       </c>
       <c r="I5" s="1">
-        <v>1</v>
+        <v>0.9999999999999768</v>
       </c>
       <c r="J5" s="1">
-        <v>0.95674099999999995</v>
+        <v>0.95674099602430218</v>
       </c>
       <c r="K5" s="1">
-        <v>0.93284500000000004</v>
+        <v>0.93284533457169527</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -982,34 +978,34 @@
         <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>0.99999899999999997</v>
+        <v>0.99999914925619082</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1">
-        <v>0.99460999999999999</v>
+        <v>0.99461035802464526</v>
       </c>
       <c r="E6" s="1">
-        <v>0.99227200000000004</v>
+        <v>0.99227213867133535</v>
       </c>
       <c r="F6" s="1">
-        <v>0.99997100000000005</v>
+        <v>0.99997110364464648</v>
       </c>
       <c r="G6" s="1">
-        <v>0.99987300000000001</v>
+        <v>0.99987345034722952</v>
       </c>
       <c r="H6" s="1">
-        <v>1</v>
+        <v>0.99999999998816957</v>
       </c>
       <c r="I6" s="1">
-        <v>1</v>
+        <v>0.99999978185052485</v>
       </c>
       <c r="J6" s="1">
-        <v>0.83829900000000002</v>
+        <v>0.83829868690613352</v>
       </c>
       <c r="K6" s="1">
-        <v>0.78655600000000003</v>
+        <v>0.78655566831850021</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -1017,34 +1013,34 @@
         <v>24</v>
       </c>
       <c r="B7" s="1">
-        <v>0.99982400000000005</v>
+        <v>0.99982440853336796</v>
       </c>
       <c r="C7" s="1">
-        <v>0.99460999999999999</v>
+        <v>0.99461035802464526</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
       </c>
       <c r="E7" s="1">
-        <v>1</v>
+        <v>0.9999999999999768</v>
       </c>
       <c r="F7" s="1">
-        <v>0.99998799999999999</v>
+        <v>0.99998777755052215</v>
       </c>
       <c r="G7" s="1">
-        <v>0.99999800000000005</v>
+        <v>0.99999844017100492</v>
       </c>
       <c r="H7" s="1">
-        <v>0.98917999999999995</v>
+        <v>0.98917952893181871</v>
       </c>
       <c r="I7" s="1">
-        <v>0.99967600000000001</v>
+        <v>0.99967579581709709</v>
       </c>
       <c r="J7" s="1">
-        <v>0.99967600000000001</v>
+        <v>0.99967579581709709</v>
       </c>
       <c r="K7" s="1">
-        <v>0.99904199999999999</v>
+        <v>0.99904236546211234</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -1052,34 +1048,34 @@
         <v>20</v>
       </c>
       <c r="B8" s="1">
-        <v>0.99967600000000001</v>
+        <v>0.99967579581709709</v>
       </c>
       <c r="C8" s="1">
-        <v>0.99227200000000004</v>
+        <v>0.99227213867133535</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
+        <v>0.9999999999999768</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>0.99997100000000005</v>
+        <v>0.99997110364464648</v>
       </c>
       <c r="G8" s="1">
-        <v>0.99999499999999997</v>
+        <v>0.99999534182073624</v>
       </c>
       <c r="H8" s="1">
-        <v>0.98517699999999997</v>
+        <v>0.98517680990115508</v>
       </c>
       <c r="I8" s="1">
-        <v>0.99943000000000004</v>
+        <v>0.99943047105928806</v>
       </c>
       <c r="J8" s="1">
-        <v>0.99982400000000005</v>
+        <v>0.99982440853336796</v>
       </c>
       <c r="K8" s="1">
-        <v>0.99943000000000004</v>
+        <v>0.99943047105928806</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -1087,34 +1083,34 @@
         <v>17</v>
       </c>
       <c r="B9" s="1">
-        <v>1</v>
+        <v>0.99999999820927599</v>
       </c>
       <c r="C9" s="1">
-        <v>0.99997100000000005</v>
+        <v>0.99997110364464648</v>
       </c>
       <c r="D9" s="1">
-        <v>0.99998799999999999</v>
+        <v>0.99998777755052215</v>
       </c>
       <c r="E9" s="1">
-        <v>0.99997100000000005</v>
+        <v>0.99997110364464648</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>0.99999999998816957</v>
       </c>
       <c r="H9" s="1">
-        <v>0.99987300000000001</v>
+        <v>0.99987345034722952</v>
       </c>
       <c r="I9" s="1">
-        <v>1</v>
+        <v>0.99999998308627969</v>
       </c>
       <c r="J9" s="1">
-        <v>0.98278299999999996</v>
+        <v>0.98278293424552976</v>
       </c>
       <c r="K9" s="1">
-        <v>0.97009900000000004</v>
+        <v>0.97009861803163855</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -1122,34 +1118,34 @@
         <v>34</v>
       </c>
       <c r="B10" s="1">
-        <v>1</v>
+        <v>0.99999989913505405</v>
       </c>
       <c r="C10" s="1">
-        <v>0.99987300000000001</v>
+        <v>0.99987345034722952</v>
       </c>
       <c r="D10" s="1">
-        <v>0.99999800000000005</v>
+        <v>0.99999844017100492</v>
       </c>
       <c r="E10" s="1">
-        <v>0.99999499999999997</v>
+        <v>0.99999534182073624</v>
       </c>
       <c r="F10" s="1">
-        <v>1</v>
+        <v>0.99999999998816957</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
       </c>
       <c r="H10" s="1">
-        <v>0.99956800000000001</v>
+        <v>0.99956779065082901</v>
       </c>
       <c r="I10" s="1">
-        <v>1</v>
+        <v>0.99999955731699297</v>
       </c>
       <c r="J10" s="1">
-        <v>0.99082999999999999</v>
+        <v>0.99082960722204561</v>
       </c>
       <c r="K10" s="1">
-        <v>0.98278299999999996</v>
+        <v>0.98278293424552987</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -1157,34 +1153,34 @@
         <v>21</v>
       </c>
       <c r="B11" s="1">
-        <v>0.99999199999999999</v>
+        <v>0.99999234504534296</v>
       </c>
       <c r="C11" s="1">
-        <v>1</v>
+        <v>0.99999999998816957</v>
       </c>
       <c r="D11" s="1">
-        <v>0.98917999999999995</v>
+        <v>0.98917952893181871</v>
       </c>
       <c r="E11" s="1">
-        <v>0.98517699999999997</v>
+        <v>0.98517680990115508</v>
       </c>
       <c r="F11" s="1">
-        <v>0.99987300000000001</v>
+        <v>0.99987345034722952</v>
       </c>
       <c r="G11" s="1">
-        <v>0.99956800000000001</v>
+        <v>0.99956779065082901</v>
       </c>
       <c r="H11" s="1">
         <v>1</v>
       </c>
       <c r="I11" s="1">
-        <v>0.99999700000000002</v>
+        <v>0.9999972551951255</v>
       </c>
       <c r="J11" s="1">
-        <v>0.78655600000000003</v>
+        <v>0.78655566831850021</v>
       </c>
       <c r="K11" s="1">
-        <v>0.72807900000000003</v>
+        <v>0.72807875120347931</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -1192,34 +1188,34 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1</v>
+        <v>0.9999999999999768</v>
       </c>
       <c r="C12" s="1">
-        <v>1</v>
+        <v>0.99999978185052485</v>
       </c>
       <c r="D12" s="1">
-        <v>0.99967600000000001</v>
+        <v>0.99967579581709709</v>
       </c>
       <c r="E12" s="1">
-        <v>0.99943000000000004</v>
+        <v>0.99943047105928806</v>
       </c>
       <c r="F12" s="1">
-        <v>1</v>
+        <v>0.99999998308627969</v>
       </c>
       <c r="G12" s="1">
-        <v>1</v>
+        <v>0.99999955731699297</v>
       </c>
       <c r="H12" s="1">
-        <v>0.99999700000000002</v>
+        <v>0.9999972551951255</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
       </c>
       <c r="J12" s="1">
-        <v>0.94571700000000003</v>
+        <v>0.94571690609545178</v>
       </c>
       <c r="K12" s="1">
-        <v>0.91802300000000003</v>
+        <v>0.91802330049418557</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -1227,34 +1223,34 @@
         <v>35</v>
       </c>
       <c r="B13" s="1">
-        <v>0.95674099999999995</v>
+        <v>0.95674099602430218</v>
       </c>
       <c r="C13" s="1">
-        <v>0.83829900000000002</v>
+        <v>0.83829868690613352</v>
       </c>
       <c r="D13" s="1">
-        <v>0.99967600000000001</v>
+        <v>0.99967579581709709</v>
       </c>
       <c r="E13" s="1">
-        <v>0.99982400000000005</v>
+        <v>0.99982440853336796</v>
       </c>
       <c r="F13" s="1">
-        <v>0.98278299999999996</v>
+        <v>0.98278293424552976</v>
       </c>
       <c r="G13" s="1">
-        <v>0.99082999999999999</v>
+        <v>0.99082960722204561</v>
       </c>
       <c r="H13" s="1">
-        <v>0.78655600000000003</v>
+        <v>0.78655566831850021</v>
       </c>
       <c r="I13" s="1">
-        <v>0.94571700000000003</v>
+        <v>0.94571690609545178</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>1</v>
+        <v>0.99999999998816957</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -1262,31 +1258,31 @@
         <v>26</v>
       </c>
       <c r="B14" s="1">
-        <v>0.93284500000000004</v>
+        <v>0.93284533457169527</v>
       </c>
       <c r="C14" s="1">
-        <v>0.78655600000000003</v>
+        <v>0.78655566831850021</v>
       </c>
       <c r="D14" s="1">
-        <v>0.99904199999999999</v>
+        <v>0.99904236546211234</v>
       </c>
       <c r="E14" s="1">
-        <v>0.99943000000000004</v>
+        <v>0.99943047105928806</v>
       </c>
       <c r="F14" s="1">
-        <v>0.97009900000000004</v>
+        <v>0.97009861803163855</v>
       </c>
       <c r="G14" s="1">
-        <v>0.98278299999999996</v>
+        <v>0.98278293424552987</v>
       </c>
       <c r="H14" s="1">
-        <v>0.72807900000000003</v>
+        <v>0.72807875120347931</v>
       </c>
       <c r="I14" s="1">
-        <v>0.91802300000000003</v>
+        <v>0.91802330049418557</v>
       </c>
       <c r="J14" s="1">
-        <v>1</v>
+        <v>0.99999999998816957</v>
       </c>
       <c r="K14" s="1">
         <v>1</v>
@@ -1301,6 +1297,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="11" width="18.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1347,31 +1346,31 @@
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>1</v>
+        <v>0.99999999408939666</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
+        <v>0.99999955731699297</v>
       </c>
       <c r="E5" s="1">
-        <v>1</v>
+        <v>0.99999989913505405</v>
       </c>
       <c r="F5" s="1">
-        <v>0.99987300000000001</v>
+        <v>0.99987345034722952</v>
       </c>
       <c r="G5" s="1">
-        <v>0.99990999999999997</v>
+        <v>0.99991018563920997</v>
       </c>
       <c r="H5" s="1">
-        <v>1</v>
+        <v>0.99999999408939666</v>
       </c>
       <c r="I5" s="1">
-        <v>1</v>
+        <v>0.99999999991226096</v>
       </c>
       <c r="J5" s="1">
-        <v>0.758073</v>
+        <v>0.75807310428104424</v>
       </c>
       <c r="K5" s="1">
-        <v>0.98917999999999995</v>
+        <v>0.98917952893181893</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -1379,34 +1378,34 @@
         <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>1</v>
+        <v>0.99999999408939666</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1">
-        <v>1</v>
+        <v>0.99999999991226096</v>
       </c>
       <c r="E6" s="1">
-        <v>0.99998799999999999</v>
+        <v>0.99998777755052215</v>
       </c>
       <c r="F6" s="1">
-        <v>0.99999499999999997</v>
+        <v>0.99999534182073624</v>
       </c>
       <c r="G6" s="1">
-        <v>0.99999700000000002</v>
+        <v>0.9999972551951255</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
       </c>
       <c r="I6" s="1">
-        <v>1</v>
+        <v>0.99999999999910849</v>
       </c>
       <c r="J6" s="1">
-        <v>0.86129800000000001</v>
+        <v>0.86129821742685508</v>
       </c>
       <c r="K6" s="1">
-        <v>0.99758100000000005</v>
+        <v>0.9975805785087104</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -1414,34 +1413,34 @@
         <v>24</v>
       </c>
       <c r="B7" s="1">
-        <v>1</v>
+        <v>0.99999955731699297</v>
       </c>
       <c r="C7" s="1">
-        <v>1</v>
+        <v>0.99999999991226096</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
       </c>
       <c r="E7" s="1">
-        <v>0.99990999999999997</v>
+        <v>0.99991018563920997</v>
       </c>
       <c r="F7" s="1">
-        <v>1</v>
+        <v>0.99999978185052485</v>
       </c>
       <c r="G7" s="1">
-        <v>1</v>
+        <v>0.99999989913505405</v>
       </c>
       <c r="H7" s="1">
-        <v>1</v>
+        <v>0.99999999991226096</v>
       </c>
       <c r="I7" s="1">
-        <v>1</v>
+        <v>0.99999999408939666</v>
       </c>
       <c r="J7" s="1">
-        <v>0.90985700000000003</v>
+        <v>0.9098567737549077</v>
       </c>
       <c r="K7" s="1">
-        <v>0.99925799999999998</v>
+        <v>0.99925767961724543</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -1449,34 +1448,34 @@
         <v>20</v>
       </c>
       <c r="B8" s="1">
-        <v>1</v>
+        <v>0.99999989913505405</v>
       </c>
       <c r="C8" s="1">
-        <v>0.99998799999999999</v>
+        <v>0.99998777755052215</v>
       </c>
       <c r="D8" s="1">
-        <v>0.99990999999999997</v>
+        <v>0.99991018563920997</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>0.99758100000000005</v>
+        <v>0.9975805785087104</v>
       </c>
       <c r="G8" s="1">
-        <v>0.99805600000000005</v>
+        <v>0.99805621709001413</v>
       </c>
       <c r="H8" s="1">
-        <v>0.99998799999999999</v>
+        <v>0.99998777755052215</v>
       </c>
       <c r="I8" s="1">
-        <v>0.99999700000000002</v>
+        <v>0.9999972551951255</v>
       </c>
       <c r="J8" s="1">
-        <v>0.58037499999999997</v>
+        <v>0.58037466261484805</v>
       </c>
       <c r="K8" s="1">
-        <v>0.95145199999999996</v>
+        <v>0.95145240767082273</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -1484,16 +1483,16 @@
         <v>17</v>
       </c>
       <c r="B9" s="1">
-        <v>0.99987300000000001</v>
+        <v>0.99987345034722952</v>
       </c>
       <c r="C9" s="1">
-        <v>0.99999499999999997</v>
+        <v>0.99999534182073624</v>
       </c>
       <c r="D9" s="1">
-        <v>1</v>
+        <v>0.99999978185052485</v>
       </c>
       <c r="E9" s="1">
-        <v>0.99758100000000005</v>
+        <v>0.9975805785087104</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
@@ -1502,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="H9" s="1">
-        <v>0.99999499999999997</v>
+        <v>0.99999534182073624</v>
       </c>
       <c r="I9" s="1">
-        <v>0.99998100000000001</v>
+        <v>0.99998098462237883</v>
       </c>
       <c r="J9" s="1">
-        <v>0.977105</v>
+        <v>0.97710480147439749</v>
       </c>
       <c r="K9" s="1">
-        <v>0.99998799999999999</v>
+        <v>0.99998777755052215</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -1519,16 +1518,16 @@
         <v>34</v>
       </c>
       <c r="B10" s="1">
-        <v>0.99990999999999997</v>
+        <v>0.99991018563920997</v>
       </c>
       <c r="C10" s="1">
-        <v>0.99999700000000002</v>
+        <v>0.9999972551951255</v>
       </c>
       <c r="D10" s="1">
-        <v>1</v>
+        <v>0.99999989913505405</v>
       </c>
       <c r="E10" s="1">
-        <v>0.99805600000000005</v>
+        <v>0.99805621709001413</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
@@ -1537,16 +1536,16 @@
         <v>1</v>
       </c>
       <c r="H10" s="1">
-        <v>0.99999700000000002</v>
+        <v>0.9999972551951255</v>
       </c>
       <c r="I10" s="1">
-        <v>0.99998799999999999</v>
+        <v>0.99998777755052215</v>
       </c>
       <c r="J10" s="1">
-        <v>0.97377800000000003</v>
+        <v>0.97377819244206809</v>
       </c>
       <c r="K10" s="1">
-        <v>0.99998100000000001</v>
+        <v>0.99998098462237883</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -1554,34 +1553,34 @@
         <v>21</v>
       </c>
       <c r="B11" s="1">
-        <v>1</v>
+        <v>0.99999999408939666</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>1</v>
+        <v>0.99999999991226096</v>
       </c>
       <c r="E11" s="1">
-        <v>0.99998799999999999</v>
+        <v>0.99998777755052215</v>
       </c>
       <c r="F11" s="1">
-        <v>0.99999499999999997</v>
+        <v>0.99999534182073624</v>
       </c>
       <c r="G11" s="1">
-        <v>0.99999700000000002</v>
+        <v>0.9999972551951255</v>
       </c>
       <c r="H11" s="1">
         <v>1</v>
       </c>
       <c r="I11" s="1">
-        <v>1</v>
+        <v>0.99999999999910849</v>
       </c>
       <c r="J11" s="1">
-        <v>0.86129800000000001</v>
+        <v>0.86129821742685508</v>
       </c>
       <c r="K11" s="1">
-        <v>0.99758100000000005</v>
+        <v>0.9975805785087104</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -1589,34 +1588,34 @@
         <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>1</v>
+        <v>0.99999999991226096</v>
       </c>
       <c r="C12" s="1">
-        <v>1</v>
+        <v>0.99999999999910849</v>
       </c>
       <c r="D12" s="1">
-        <v>1</v>
+        <v>0.99999999408939666</v>
       </c>
       <c r="E12" s="1">
-        <v>0.99999700000000002</v>
+        <v>0.9999972551951255</v>
       </c>
       <c r="F12" s="1">
-        <v>0.99998100000000001</v>
+        <v>0.99998098462237883</v>
       </c>
       <c r="G12" s="1">
-        <v>0.99998799999999999</v>
+        <v>0.99998777755052215</v>
       </c>
       <c r="H12" s="1">
-        <v>1</v>
+        <v>0.99999999999910849</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
       </c>
       <c r="J12" s="1">
-        <v>0.82606100000000005</v>
+        <v>0.82606061700015176</v>
       </c>
       <c r="K12" s="1">
-        <v>0.99554200000000004</v>
+        <v>0.99554185494885816</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -1624,34 +1623,34 @@
         <v>35</v>
       </c>
       <c r="B13" s="1">
-        <v>0.758073</v>
+        <v>0.75807310428104424</v>
       </c>
       <c r="C13" s="1">
-        <v>0.86129800000000001</v>
+        <v>0.86129821742685508</v>
       </c>
       <c r="D13" s="1">
-        <v>0.90985700000000003</v>
+        <v>0.9098567737549077</v>
       </c>
       <c r="E13" s="1">
-        <v>0.58037499999999997</v>
+        <v>0.58037466261484805</v>
       </c>
       <c r="F13" s="1">
-        <v>0.977105</v>
+        <v>0.97710480147439749</v>
       </c>
       <c r="G13" s="1">
-        <v>0.97377800000000003</v>
+        <v>0.97377819244206809</v>
       </c>
       <c r="H13" s="1">
-        <v>0.86129800000000001</v>
+        <v>0.86129821742685508</v>
       </c>
       <c r="I13" s="1">
-        <v>0.82606100000000005</v>
+        <v>0.82606061700015176</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>0.99943000000000004</v>
+        <v>0.99943047105928806</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -1659,31 +1658,31 @@
         <v>26</v>
       </c>
       <c r="B14" s="1">
-        <v>0.98917999999999995</v>
+        <v>0.98917952893181893</v>
       </c>
       <c r="C14" s="1">
-        <v>0.99758100000000005</v>
+        <v>0.9975805785087104</v>
       </c>
       <c r="D14" s="1">
-        <v>0.99925799999999998</v>
+        <v>0.99925767961724543</v>
       </c>
       <c r="E14" s="1">
-        <v>0.95145199999999996</v>
+        <v>0.95145240767082273</v>
       </c>
       <c r="F14" s="1">
-        <v>0.99998799999999999</v>
+        <v>0.99998777755052215</v>
       </c>
       <c r="G14" s="1">
-        <v>0.99998100000000001</v>
+        <v>0.99998098462237883</v>
       </c>
       <c r="H14" s="1">
-        <v>0.99758100000000005</v>
+        <v>0.9975805785087104</v>
       </c>
       <c r="I14" s="1">
-        <v>0.99554200000000004</v>
+        <v>0.99554185494885816</v>
       </c>
       <c r="J14" s="1">
-        <v>0.99943000000000004</v>
+        <v>0.99943047105928806</v>
       </c>
       <c r="K14" s="1">
         <v>1</v>
@@ -1699,7 +1698,7 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="18.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -1722,41 +1721,41 @@
       <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3">
-        <v>5.4501000000000001E-2</v>
-      </c>
-      <c r="D5" s="3">
-        <v>3.0991000000000001E-2</v>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>5.4500630114282862E-2</v>
+      </c>
+      <c r="D5" s="1">
+        <v>3.0991162591187279E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="3">
-        <v>5.4501000000000001E-2</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3">
-        <v>3.9999999999999998E-6</v>
+      <c r="B6" s="1">
+        <v>5.4500630114282862E-2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3.9727329548269998E-6</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="3">
-        <v>3.0991000000000001E-2</v>
-      </c>
-      <c r="C7" s="3">
-        <v>3.9999999999999998E-6</v>
-      </c>
-      <c r="D7" s="3">
+      <c r="B7" s="1">
+        <v>3.0991162591187279E-2</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3.9727329548269998E-6</v>
+      </c>
+      <c r="D7" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1770,7 +1769,7 @@
   <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="18.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
@@ -1814,349 +1813,349 @@
       <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2">
-        <v>8.3719999999999992E-3</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.90985700000000003</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1.6584999999999999E-2</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.93284500000000004</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0.14849000000000001</v>
-      </c>
-      <c r="H5" s="2">
-        <v>8.5057999999999995E-2</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0.91802300000000003</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0.91802300000000003</v>
-      </c>
-      <c r="K5" s="2">
-        <v>1</v>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>8.3719467633767142E-3</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.9098567737549077</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1.6584839573062001E-2</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.93284533457169527</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.1484899861323625</v>
+      </c>
+      <c r="H5" s="1">
+        <v>8.505818802908327E-2</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.91802330049418557</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.91802330049418557</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0.9999999999999768</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2">
-        <v>8.3719999999999992E-3</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.42862699999999998</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.380857</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0.99554200000000004</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0.99943000000000004</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0.412464</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0.412464</v>
-      </c>
-      <c r="K6" s="2">
-        <v>7.0070000000000002E-3</v>
+      <c r="B6" s="1">
+        <v>8.3719467633767142E-3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.42862699325342252</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.99999999408939666</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.38085671934274662</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.99554185494885816</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.99943047105928806</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.41246352866489311</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.41246352866489311</v>
+      </c>
+      <c r="K6" s="1">
+        <v>7.0074238418840196E-3</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="2">
-        <v>0.90985700000000003</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0.42862699999999998</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0.56329600000000002</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0.95145199999999996</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0.88227</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0.89198299999999997</v>
+      <c r="B7" s="1">
+        <v>0.9098567737549077</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.42862699325342252</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.56329613169267367</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.99999999999910849</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.95145240767082251</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.88227014030235773</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0.8919827960942216</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="2">
-        <v>1.6584999999999999E-2</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0.56329600000000002</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0.51208900000000002</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0.99925799999999998</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0.99995699999999998</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0.54620100000000005</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0.54620100000000005</v>
-      </c>
-      <c r="K8" s="2">
-        <v>1.4038999999999999E-2</v>
+      <c r="B8" s="1">
+        <v>1.6584839573062001E-2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.99999999408939666</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.56329613169267367</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.51208856212633047</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.99925767961724543</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0.99995701813841065</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.54620144354668509</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0.54620144354668509</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1.4039202332943311E-2</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="2">
-        <v>0.93284500000000004</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0.380857</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.51208900000000002</v>
-      </c>
-      <c r="F9" s="2">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0.93284500000000004</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0.85004800000000003</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2">
-        <v>0.91802300000000003</v>
+      <c r="B9" s="1">
+        <v>0.93284533457169527</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.38085671934274662</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.99999999999910849</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.51208856212633047</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.93284533457169494</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.85004809609552079</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.9999999999999768</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0.9999999999999768</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0.91802330049418557</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="2">
-        <v>0.14849000000000001</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0.99554200000000004</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0.95145199999999996</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0.99925799999999998</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0.93284500000000004</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0.94571700000000003</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0.94571700000000003</v>
-      </c>
-      <c r="K10" s="2">
-        <v>0.13197700000000001</v>
+      <c r="B10" s="1">
+        <v>0.1484899861323625</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.99554185494885816</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.95145240767082251</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.99925767961724543</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.93284533457169494</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.99999998308627969</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.94571690609545178</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.94571690609545178</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0.131977120277986</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="2">
-        <v>8.5057999999999995E-2</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0.99943000000000004</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0.88227</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.99995699999999998</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0.85004800000000003</v>
-      </c>
-      <c r="G11" s="2">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0.87204099999999996</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0.87204099999999996</v>
-      </c>
-      <c r="K11" s="2">
-        <v>7.4468000000000006E-2</v>
+      <c r="B11" s="1">
+        <v>8.505818802908327E-2</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.99943047105928806</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.88227014030235773</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.99995701813841065</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.85004809609552079</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0.99999998308627969</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.87204082905245106</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.87204082905245106</v>
+      </c>
+      <c r="K11" s="1">
+        <v>7.4467709090946688E-2</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="2">
-        <v>0.91802300000000003</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0.412464</v>
-      </c>
-      <c r="D12" s="2">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0.54620100000000005</v>
-      </c>
-      <c r="F12" s="2">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0.94571700000000003</v>
-      </c>
-      <c r="H12" s="2">
-        <v>0.87204099999999996</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1</v>
-      </c>
-      <c r="K12" s="2">
-        <v>0.90117800000000003</v>
+      <c r="B12" s="1">
+        <v>0.91802330049418557</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.41246352866489311</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.54620144354668509</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.9999999999999768</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.94571690609545178</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.87204082905245106</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0.9011778596711113</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2">
-        <v>0.91802300000000003</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0.412464</v>
-      </c>
-      <c r="D13" s="2">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0.54620100000000005</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0.94571700000000003</v>
-      </c>
-      <c r="H13" s="2">
-        <v>0.87204099999999996</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2">
-        <v>1</v>
-      </c>
-      <c r="K13" s="2">
-        <v>0.90117800000000003</v>
+      <c r="B13" s="1">
+        <v>0.91802330049418557</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.41246352866489311</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.54620144354668509</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0.9999999999999768</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0.94571690609545178</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0.87204082905245106</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0.9011778596711113</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="2">
-        <v>1</v>
-      </c>
-      <c r="C14" s="2">
-        <v>7.0070000000000002E-3</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0.89198299999999997</v>
-      </c>
-      <c r="E14" s="2">
-        <v>1.4038999999999999E-2</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0.91802300000000003</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0.13197700000000001</v>
-      </c>
-      <c r="H14" s="2">
-        <v>7.4468000000000006E-2</v>
-      </c>
-      <c r="I14" s="2">
-        <v>0.90117800000000003</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0.90117800000000003</v>
-      </c>
-      <c r="K14" s="2">
+      <c r="B14" s="1">
+        <v>0.9999999999999768</v>
+      </c>
+      <c r="C14" s="1">
+        <v>7.0074238418840196E-3</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.8919827960942216</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1.4039202332943311E-2</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0.91802330049418557</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0.131977120277986</v>
+      </c>
+      <c r="H14" s="1">
+        <v>7.4467709090946688E-2</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0.9011778596711113</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.9011778596711113</v>
+      </c>
+      <c r="K14" s="1">
         <v>1</v>
       </c>
     </row>
